--- a/data/trans_orig/IP05A06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP05A06-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97875</t>
+          <t>97572</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115069</t>
+          <t>114825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97070</t>
+          <t>96025</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114765</t>
+          <t>113453</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>199505</t>
+          <t>200488</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>225667</t>
+          <t>225781</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,12%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>26444</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42029</t>
+          <t>42741</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26547</t>
+          <t>27575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43189</t>
+          <t>44042</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55674</t>
+          <t>56990</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81225</t>
+          <t>81190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>9809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148010</t>
+          <t>148236</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172624</t>
+          <t>172719</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179075</t>
+          <t>176862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>202594</t>
+          <t>201315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334770</t>
+          <t>333882</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>368450</t>
+          <t>368159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59753</t>
+          <t>58765</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84115</t>
+          <t>82322</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>56341</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79313</t>
+          <t>80262</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>121384</t>
+          <t>120152</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>154058</t>
+          <t>154744</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19763</t>
+          <t>19574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104078</t>
+          <t>103771</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122058</t>
+          <t>122071</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100720</t>
+          <t>100485</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>119652</t>
+          <t>119241</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>209567</t>
+          <t>209714</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>235995</t>
+          <t>236900</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,85%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29864</t>
+          <t>29572</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>47085</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35651</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54441</t>
+          <t>54393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70316</t>
+          <t>70091</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95625</t>
+          <t>96066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110446</t>
+          <t>109114</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>130068</t>
+          <t>130152</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123681</t>
+          <t>124600</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142935</t>
+          <t>142925</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>241324</t>
+          <t>242505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266991</t>
+          <t>268428</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34301</t>
+          <t>34191</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52423</t>
+          <t>54054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30853</t>
+          <t>31240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48149</t>
+          <t>49058</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70634</t>
+          <t>70003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95375</t>
+          <t>95036</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11646</t>
+          <t>11407</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>18701</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>481977</t>
+          <t>480324</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>522132</t>
+          <t>519340</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>521058</t>
+          <t>521551</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>561508</t>
+          <t>560616</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1012527</t>
+          <t>1013972</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1071009</t>
+          <t>1072720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>165609</t>
+          <t>167126</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>203476</t>
+          <t>205417</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>165371</t>
+          <t>165931</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>205451</t>
+          <t>205967</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>345253</t>
+          <t>344436</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>400772</t>
+          <t>400251</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27784</t>
+          <t>28671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>16043</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31790</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32682</t>
+          <t>33583</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53786</t>
+          <t>54020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94653</t>
+          <t>93872</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109192</t>
+          <t>109349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94388</t>
+          <t>94410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108338</t>
+          <t>108372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>193329</t>
+          <t>193322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213118</t>
+          <t>213818</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30310</t>
+          <t>30976</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>14324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27411</t>
+          <t>27230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34547</t>
+          <t>33614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53361</t>
+          <t>53527</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>149707</t>
+          <t>150145</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>169518</t>
+          <t>169104</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180552</t>
+          <t>181427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>204029</t>
+          <t>204003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>339177</t>
+          <t>337656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>368509</t>
+          <t>367299</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34480</t>
+          <t>34647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52772</t>
+          <t>53569</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45416</t>
+          <t>46119</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67401</t>
+          <t>67425</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>84769</t>
+          <t>86468</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>113969</t>
+          <t>114225</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>8696</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>13085</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>134926</t>
+          <t>133962</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>152581</t>
+          <t>153232</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>129112</t>
+          <t>129434</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148781</t>
+          <t>149083</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>270307</t>
+          <t>269193</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>297724</t>
+          <t>298046</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30538</t>
+          <t>30720</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48139</t>
+          <t>48892</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28915</t>
+          <t>28953</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47214</t>
+          <t>46238</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62487</t>
+          <t>63744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88695</t>
+          <t>91283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9621</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22116</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111106</t>
+          <t>112433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131199</t>
+          <t>132240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121311</t>
+          <t>121427</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>139695</t>
+          <t>141311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>239079</t>
+          <t>238242</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>267099</t>
+          <t>267100</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34304</t>
+          <t>32804</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53108</t>
+          <t>52183</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>25579</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43838</t>
+          <t>43996</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64067</t>
+          <t>64472</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90506</t>
+          <t>91464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13319</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15038</t>
+          <t>14094</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23333</t>
+          <t>22587</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>509154</t>
+          <t>510973</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>544977</t>
+          <t>547347</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>547125</t>
+          <t>545335</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>583631</t>
+          <t>583776</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1067061</t>
+          <t>1067112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1119577</t>
+          <t>1120447</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,7%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>131602</t>
+          <t>130626</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>166175</t>
+          <t>164966</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>130923</t>
+          <t>130996</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>165223</t>
+          <t>166622</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>273079</t>
+          <t>272046</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>322383</t>
+          <t>322596</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>16855</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32281</t>
+          <t>32600</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36990</t>
+          <t>37074</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40911</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64542</t>
+          <t>65249</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42402</t>
+          <t>42343</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>51259</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44487</t>
+          <t>44284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53915</t>
+          <t>53888</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90362</t>
+          <t>90495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102862</t>
+          <t>103517</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10674</t>
+          <t>10815</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14596</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123037</t>
+          <t>123674</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139197</t>
+          <t>139566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135717</t>
+          <t>134447</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>154332</t>
+          <t>153669</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>264763</t>
+          <t>265395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>288060</t>
+          <t>288818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22786</t>
+          <t>22871</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16535</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32472</t>
+          <t>32896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30351</t>
+          <t>29660</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50752</t>
+          <t>51450</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20201</t>
+          <t>20492</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>32776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>130306</t>
+          <t>129600</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>150896</t>
+          <t>151219</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164883</t>
+          <t>164091</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>186729</t>
+          <t>185800</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>302026</t>
+          <t>301119</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>333301</t>
+          <t>332834</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37069</t>
+          <t>36871</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37845</t>
+          <t>39724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37471</t>
+          <t>39044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68973</t>
+          <t>69913</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14617</t>
+          <t>14677</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22141</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145626</t>
+          <t>148705</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>235483</t>
+          <t>235222</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>250364</t>
+          <t>249047</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>274843</t>
+          <t>274800</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>394681</t>
+          <t>402223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>501843</t>
+          <t>502235</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,51%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21464</t>
+          <t>20682</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>41640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>20352</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40457</t>
+          <t>41589</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45843</t>
+          <t>45872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74496</t>
+          <t>77015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>105647</t>
+          <t>104430</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20631</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>140734</t>
+          <t>124966</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>457389</t>
+          <t>454155</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>559959</t>
+          <t>560814</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>614974</t>
+          <t>614706</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>654875</t>
+          <t>656060</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1078915</t>
+          <t>1095391</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1199255</t>
+          <t>1200342</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64543</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95937</t>
+          <t>96166</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69007</t>
+          <t>67849</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>104579</t>
+          <t>103397</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>141307</t>
+          <t>141994</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>188818</t>
+          <t>191392</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135692</t>
+          <t>139205</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28760</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50755</t>
+          <t>49983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62840</t>
+          <t>62505</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>192037</t>
+          <t>182731</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP05A06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP05A06-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>105930</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>96724</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>114648</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>72,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>66,25%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,53%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>107023</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>97572</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>114825</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>97469</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>115337</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>72,92%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>66,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>105930</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>96025</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>113453</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>72,56%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>200488</t>
+          <t>200326</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>225781</t>
+          <t>226205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34824</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26496</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>43926</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30,09%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>33414</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26444</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>42741</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25426</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>42344</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>22,77%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,12%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>34824</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>27575</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>44042</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>23,85%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56990</t>
+          <t>56785</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81190</t>
+          <t>79988</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5237</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9721</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6324</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3092</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11093</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3195</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11855</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,31%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5237</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2573</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9809</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>18540</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>191029</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>178948</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>204061</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>71,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>67,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>76,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>160437</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>148236</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>172719</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>148001</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>171965</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>68,09%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>62,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>73,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>191029</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>176862</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>201315</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>71,65%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>333882</t>
+          <t>334954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>368159</t>
+          <t>367507</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,17%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67368</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>55287</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>79422</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>25,27%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>20,74%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>29,79%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>70766</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>58765</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>82322</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>82563</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>30,03%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>24,94%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>34,94%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>67368</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>56341</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>80262</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>25,27%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>120152</t>
+          <t>122858</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>154744</t>
+          <t>155107</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8223</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4316</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13871</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4436</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1540</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9553</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1511</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8793</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,88%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8223</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4648</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13597</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19574</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>266620</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>266620</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>266620</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>339</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>235639</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>235639</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>235639</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>266620</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>266620</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>266620</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>110156</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99692</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>118366</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>69,89%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>63,25%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>75,1%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>112896</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>103771</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>122071</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>103456</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>121630</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>72,97%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>67,07%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>78,9%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>110156</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>100485</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>119241</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>69,89%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>209714</t>
+          <t>209220</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236900</t>
+          <t>235873</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>44819</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36388</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>55204</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>23,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>35,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>38286</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29572</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>47085</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30053</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>48313</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>24,75%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,11%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>30,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>44819</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>36173</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>54393</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>28,43%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70091</t>
+          <t>71406</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96066</t>
+          <t>97026</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6970</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>3534</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8001</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8228</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6309</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>12704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>157620</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>157620</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>157620</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>154716</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>154716</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>154716</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>157620</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>157620</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>157620</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>134832</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>125290</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>143850</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>74,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>120580</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>109114</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>130152</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>109815</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>129492</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>71,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>64,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>134832</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>124600</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>142925</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>74,93%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>242505</t>
+          <t>241621</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>268428</t>
+          <t>268152</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,68%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>38929</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>29786</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>47321</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>21,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>26,3%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43330</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>34191</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>54054</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>34790</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>53709</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>25,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>31,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>38929</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>31240</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>49058</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70003</t>
+          <t>69490</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95036</t>
+          <t>95477</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -2316,107 +2316,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6193</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3254</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11910</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>5841</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2718</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10405</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2777</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>11013</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,44%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>6193</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2901</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>11407</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>12034</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>7188</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>18370</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>3,44%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>12034</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>7087</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>18701</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>169751</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>169751</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>169751</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2546,72 +2546,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>541946</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>520440</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>561708</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>72,24%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>69,37%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>74,88%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>722</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>500936</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>480324</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>519340</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>480038</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>519877</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>70,87%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>67,95%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>73,47%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>541946</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>521551</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>560616</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>72,24%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1013972</t>
+          <t>1015281</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1072720</t>
+          <t>1072207</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -2664,102 +2664,102 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>185940</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>166440</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>206480</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>24,79%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>22,19%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>27,52%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
           <t>185795</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>167126</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>205417</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>167764</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>206091</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>26,28%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>23,73%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>29,16%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>371735</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>344406</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>398593</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>25,51%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>23,64%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>29,06%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>185940</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>165931</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>205967</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>24,79%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>22,12%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>27,46%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>371735</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>344436</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>400251</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>25,51%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>23,64%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -2772,72 +2772,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>22298</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15430</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>30943</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>20134</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>13796</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>28671</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>13684</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>28845</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2,85%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>22298</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>16043</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>31349</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33583</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54020</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2885,57 +2885,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>750184</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>750184</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>750184</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1019</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>706866</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>706866</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>706866</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>750184</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>750184</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>750184</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3066,7 +3066,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>101901</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>94695</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>108221</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>82,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>76,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>87,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>101976</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>93872</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>109349</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>94185</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>109172</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>77,46%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>71,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>101901</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>94410</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>108372</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>82,07%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>193322</t>
+          <t>192827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213818</t>
+          <t>214116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,7%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20276</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14250</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27576</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>22,21%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22877</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16768</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30976</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16279</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>30330</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>17,38%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>23,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20276</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14324</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27230</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33614</t>
+          <t>33561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53527</t>
+          <t>53233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6801</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3539</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11372</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3543</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11758</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,17%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>2,69%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5301</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>192556</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>181041</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>203078</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>75,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70,56%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>160775</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>150145</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>169104</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>151260</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>170146</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>77,05%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>192556</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>181427</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>204003</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>75,05%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>337656</t>
+          <t>336541</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>367299</t>
+          <t>366855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56195</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>46000</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67379</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>21,9%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>26,26%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>43099</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>34647</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>53569</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>33822</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>51756</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>20,65%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>16,6%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>25,67%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>56195</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>46119</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>67425</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>86468</t>
+          <t>85240</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>114225</t>
+          <t>114083</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7824</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13264</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4801</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2203</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8696</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1876</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9224</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7824</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4167</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13085</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19311</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>256575</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>256575</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>256575</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>208675</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>208675</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>208675</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>256575</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>256575</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>256575</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139859</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>129588</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149337</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>75,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>69,49%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>80,08%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144163</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>133962</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>153232</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>134125</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>153242</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>76,54%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>71,12%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>81,35%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139859</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>129434</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149083</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>269193</t>
+          <t>270186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>298046</t>
+          <t>296932</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37129</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28295</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46237</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24,79%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>38980</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30720</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>48892</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30023</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>48327</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>20,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,31%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>37129</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>28953</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>46238</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63744</t>
+          <t>64315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91283</t>
+          <t>89236</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9502</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5175</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15523</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5216</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2190</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10027</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2321</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10598</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2,77%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>9502</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>5341</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>15500</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>21277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186490</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186490</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186490</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>188359</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>188359</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>188359</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186490</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186490</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186490</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4602,72 +4602,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>131330</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>120181</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>140280</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>75,46%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69,05%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>80,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>122044</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>112433</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>132240</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>112105</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>131770</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>70,9%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76,82%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>131330</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>121427</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>141311</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>75,46%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238242</t>
+          <t>239134</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>267100</t>
+          <t>266923</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -4715,72 +4715,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>34178</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>26154</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>44627</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>25,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>42918</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>32804</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>52183</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>33388</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>52599</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>24,93%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,06%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>34178</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>25579</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>43996</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>19,64%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64472</t>
+          <t>64795</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>91464</t>
+          <t>92457</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -4828,72 +4828,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8540</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4646</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>15034</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>7171</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3525</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>12438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4046</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>12434</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>8540</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4995</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>14094</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22587</t>
+          <t>22635</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -4941,57 +4941,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>172133</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>172133</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>172133</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>565645</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>547488</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>586956</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>76,31%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>73,86%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>79,18%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>798</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>528958</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>510973</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>547347</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>509882</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>546778</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>75,48%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>72,91%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>78,1%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>805</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>565645</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>545335</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>583776</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>76,31%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1067112</t>
+          <t>1067524</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1120447</t>
+          <t>1121108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -5171,72 +5171,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>147777</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>128331</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>165703</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>19,94%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>17,31%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>22,35%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>147875</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>130626</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>164966</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>130359</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>166493</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>21,1%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>147777</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>130996</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>166622</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>19,94%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>272046</t>
+          <t>271058</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>322596</t>
+          <t>322005</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -5284,72 +5284,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>27854</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20078</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>37709</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>23989</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>16855</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>32600</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>17168</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>32524</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>3,42%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>27854</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>19343</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>37074</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41939</t>
+          <t>41356</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65249</t>
+          <t>65251</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5397,57 +5397,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>741276</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>741276</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>741276</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>700822</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>700822</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>700822</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>741276</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>741276</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>741276</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5746,72 +5746,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40110</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35388</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>43853</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>79,37%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>70,02%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>47426</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>42343</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51259</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>82,46%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49900</t>
+          <t>42925</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44284</t>
+          <t>38174</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53888</t>
+          <t>46153</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5821,32 +5821,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>97326</t>
+          <t>83035</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90495</t>
+          <t>76575</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103517</t>
+          <t>88224</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -5859,67 +5859,67 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4831</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2366</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8568</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16,95%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6204</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3185</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10510</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5934,32 +5934,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -5972,72 +5972,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5596</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2856</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9756</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3881</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1651</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8132</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,14%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6047,32 +6047,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>15899</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -6085,57 +6085,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6202,72 +6202,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>124000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>115357</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>130970</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>132114</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>123674</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>139566</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>83,68%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>145045</t>
+          <t>120592</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134447</t>
+          <t>113127</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>153669</t>
+          <t>127267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6277,32 +6277,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>277160</t>
+          <t>244592</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>265395</t>
+          <t>233249</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>288818</t>
+          <t>254563</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -6315,72 +6315,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20984</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14907</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>28391</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>18,06%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>15725</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10105</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>22871</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9,96%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>14,49%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23577</t>
+          <t>14688</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6390,32 +6390,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>39302</t>
+          <t>35672</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29660</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51450</t>
+          <t>46010</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -6428,72 +6428,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12215</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7759</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18731</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10043</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6096</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15668</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>9741</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6503,32 +6503,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23584</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32776</t>
+          <t>30157</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -6541,57 +6541,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157199</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>157199</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>157199</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>157882</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>157882</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>157882</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>182164</t>
+          <t>145021</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>182164</t>
+          <t>145021</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182164</t>
+          <t>145021</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>340046</t>
+          <t>302220</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>340046</t>
+          <t>302220</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>340046</t>
+          <t>302220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6658,72 +6658,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>169132</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>159826</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>177248</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>85,33%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>80,63%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>89,42%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>141984</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>129600</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>151219</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>81,65%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>74,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>86,96%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>176494</t>
+          <t>144632</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164091</t>
+          <t>135441</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185800</t>
+          <t>152909</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6733,32 +6733,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>318478</t>
+          <t>313764</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>301119</t>
+          <t>300851</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332834</t>
+          <t>326421</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -6771,72 +6771,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21391</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14386</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30233</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25495</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17208</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36871</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26444</t>
+          <t>24617</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>17182</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39724</t>
+          <t>33809</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6846,32 +6846,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>51939</t>
+          <t>46008</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39044</t>
+          <t>34937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69913</t>
+          <t>57858</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -6889,32 +6889,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6924,32 +6924,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6959,32 +6959,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21936</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -6997,57 +6997,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>198211</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>198211</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>198211</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>210624</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>210624</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>210624</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>384512</t>
+          <t>373729</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>384512</t>
+          <t>373729</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>384512</t>
+          <t>373729</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>250859</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>236851</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>261552</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>85,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>81,02%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>89,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>209970</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>148705</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>235222</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>76,23%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,98%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>85,39%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>263556</t>
+          <t>214204</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>249047</t>
+          <t>202421</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>274800</t>
+          <t>224462</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>473524</t>
+          <t>465063</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>402223</t>
+          <t>447503</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>502235</t>
+          <t>478842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>87,24%</t>
         </is>
       </c>
     </row>
@@ -7227,72 +7227,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>29371</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21225</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>41368</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>31447</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>20682</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>41640</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>11,42%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15,12%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>32048</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41589</t>
+          <t>41507</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7302,32 +7302,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>60533</t>
+          <t>61419</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45872</t>
+          <t>49788</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77015</t>
+          <t>77524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -7340,107 +7340,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12092</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6821</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>21230</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34041</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6634</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>104430</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>37,91%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12452</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21376</t>
+          <t>21390</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>22393</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>14647</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>35463</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>46493</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>18001</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>124966</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -7453,57 +7453,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>292322</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>292322</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>292322</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>342</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>275458</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>275458</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>275458</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>305093</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>305093</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>305093</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7528,17 +7528,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>580550</t>
+          <t>548875</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>580550</t>
+          <t>548875</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>580550</t>
+          <t>548875</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>584101</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>565795</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>601647</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>83,65%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>81,03%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>86,16%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>531493</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>454155</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>560814</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>68,32%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>84,37%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>634995</t>
+          <t>522354</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>614706</t>
+          <t>506155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>656060</t>
+          <t>537882</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1166488</t>
+          <t>1106454</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1095391</t>
+          <t>1082258</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1200342</t>
+          <t>1129283</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -7683,72 +7683,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>76577</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>62287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>93238</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>78871</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>64263</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>96166</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>85303</t>
+          <t>76502</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>67849</t>
+          <t>63174</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>103397</t>
+          <t>90246</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>164174</t>
+          <t>153080</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>141994</t>
+          <t>133996</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>191392</t>
+          <t>177105</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -7796,72 +7796,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>37591</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>27844</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>49619</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>54374</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>25639</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>139205</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>20,94%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>39027</t>
+          <t>30326</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28883</t>
+          <t>21967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49983</t>
+          <t>41804</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7871,32 +7871,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>93401</t>
+          <t>67917</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62505</t>
+          <t>53384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>182731</t>
+          <t>82512</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -7909,57 +7909,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>698270</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>698270</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>698270</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>759325</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>759325</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>759325</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7984,17 +7984,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1424063</t>
+          <t>1327451</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1424063</t>
+          <t>1327451</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1424063</t>
+          <t>1327451</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
